--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N47_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N47_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.22303302034515</v>
+        <v>5.073742865806087</v>
       </c>
       <c r="D2" t="n">
-        <v>37.74147019928085</v>
+        <v>6.132988907383139</v>
       </c>
       <c r="E2" t="n">
-        <v>9.438273680618584</v>
+        <v>1.53371947310052</v>
       </c>
       <c r="F2" t="n">
-        <v>7.801738588705014</v>
+        <v>1.267782520664565</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.53379517148532</v>
+        <v>6.099241715366365</v>
       </c>
       <c r="D3" t="n">
-        <v>38.84878282894611</v>
+        <v>6.312927209703743</v>
       </c>
       <c r="E3" t="n">
-        <v>9.438273680618584</v>
+        <v>1.53371947310052</v>
       </c>
       <c r="F3" t="n">
-        <v>7.801738588705014</v>
+        <v>1.267782520664565</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.82111774856215</v>
+        <v>3.058431634141349</v>
       </c>
       <c r="D4" t="n">
-        <v>18.40989978544987</v>
+        <v>2.991608715135604</v>
       </c>
       <c r="E4" t="n">
-        <v>9.438273680618584</v>
+        <v>1.53371947310052</v>
       </c>
       <c r="F4" t="n">
-        <v>7.801738588705014</v>
+        <v>1.267782520664565</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>13.32647769743493</v>
+        <v>2.165552625833176</v>
       </c>
       <c r="D5" t="n">
-        <v>31.38896091393459</v>
+        <v>5.100706148514371</v>
       </c>
       <c r="E5" t="n">
-        <v>9.438273680618584</v>
+        <v>1.53371947310052</v>
       </c>
       <c r="F5" t="n">
-        <v>7.801738588705014</v>
+        <v>1.267782520664565</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>8.50394067903283</v>
+        <v>1.381890360342835</v>
       </c>
       <c r="D6" t="n">
-        <v>39.29360105806408</v>
+        <v>6.385210171935412</v>
       </c>
       <c r="E6" t="n">
-        <v>9.438273680618584</v>
+        <v>1.53371947310052</v>
       </c>
       <c r="F6" t="n">
-        <v>7.801738588705014</v>
+        <v>1.267782520664565</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.37355108404245</v>
+        <v>5.098202051156898</v>
       </c>
       <c r="D7" t="n">
-        <v>32.74573820029222</v>
+        <v>5.321182457547486</v>
       </c>
       <c r="E7" t="n">
-        <v>9.438273680618584</v>
+        <v>1.53371947310052</v>
       </c>
       <c r="F7" t="n">
-        <v>7.801738588705014</v>
+        <v>1.267782520664565</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>13.53698637068088</v>
+        <v>2.199760285235644</v>
       </c>
       <c r="D8" t="n">
-        <v>24.09603268206479</v>
+        <v>3.915605310835528</v>
       </c>
       <c r="E8" t="n">
-        <v>9.438273680618584</v>
+        <v>1.53371947310052</v>
       </c>
       <c r="F8" t="n">
-        <v>7.801738588705014</v>
+        <v>1.267782520664565</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>20.4169813318875</v>
+        <v>3.317759466431719</v>
       </c>
       <c r="D9" t="n">
-        <v>21.78854593952494</v>
+        <v>3.540638715172802</v>
       </c>
       <c r="E9" t="n">
-        <v>9.438273680618584</v>
+        <v>1.53371947310052</v>
       </c>
       <c r="F9" t="n">
-        <v>7.801738588705014</v>
+        <v>1.267782520664565</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>48.52595734730879</v>
+        <v>7.885468068937679</v>
       </c>
       <c r="D10" t="n">
-        <v>46.61093297454644</v>
+        <v>7.574276608363797</v>
       </c>
       <c r="E10" t="n">
-        <v>9.438273680618584</v>
+        <v>1.53371947310052</v>
       </c>
       <c r="F10" t="n">
-        <v>7.801738588705014</v>
+        <v>1.267782520664565</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>24.66779276708802</v>
+        <v>4.008516324651803</v>
       </c>
       <c r="D11" t="n">
-        <v>31.89592358572567</v>
+        <v>5.183087582680421</v>
       </c>
       <c r="E11" t="n">
-        <v>9.438273680618584</v>
+        <v>1.53371947310052</v>
       </c>
       <c r="F11" t="n">
-        <v>7.801738588705014</v>
+        <v>1.267782520664565</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>25.68611401443749</v>
+        <v>4.173993527346092</v>
       </c>
       <c r="D12" t="n">
-        <v>24.23398442612838</v>
+        <v>3.938022469245861</v>
       </c>
       <c r="E12" t="n">
-        <v>9.438273680618584</v>
+        <v>1.53371947310052</v>
       </c>
       <c r="F12" t="n">
-        <v>7.801738588705014</v>
+        <v>1.267782520664565</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>34.16792170942868</v>
+        <v>5.552287277782161</v>
       </c>
       <c r="D13" t="n">
-        <v>34.64616227805976</v>
+        <v>5.630001370184711</v>
       </c>
       <c r="E13" t="n">
-        <v>9.438273680618584</v>
+        <v>1.53371947310052</v>
       </c>
       <c r="F13" t="n">
-        <v>7.801738588705014</v>
+        <v>1.267782520664565</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>21.6537362704435</v>
+        <v>3.518732143947068</v>
       </c>
       <c r="D14" t="n">
-        <v>20.55073360292276</v>
+        <v>3.339494210474949</v>
       </c>
       <c r="E14" t="n">
-        <v>9.438273680618584</v>
+        <v>1.53371947310052</v>
       </c>
       <c r="F14" t="n">
-        <v>7.801738588705014</v>
+        <v>1.267782520664565</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>21.83412360434268</v>
+        <v>3.548045085705686</v>
       </c>
       <c r="D15" t="n">
-        <v>19.94922093752433</v>
+        <v>3.241748402347703</v>
       </c>
       <c r="E15" t="n">
-        <v>9.438273680618584</v>
+        <v>1.53371947310052</v>
       </c>
       <c r="F15" t="n">
-        <v>7.801738588705014</v>
+        <v>1.267782520664565</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>34.50206014595723</v>
+        <v>5.60658477371805</v>
       </c>
       <c r="D16" t="n">
-        <v>33.90989907015025</v>
+        <v>5.510358598899416</v>
       </c>
       <c r="E16" t="n">
-        <v>9.438273680618584</v>
+        <v>1.53371947310052</v>
       </c>
       <c r="F16" t="n">
-        <v>7.801738588705014</v>
+        <v>1.267782520664565</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>23.69505806221608</v>
+        <v>3.850446935110113</v>
       </c>
       <c r="D17" t="n">
-        <v>25.42346921864291</v>
+        <v>4.131313748029473</v>
       </c>
       <c r="E17" t="n">
-        <v>9.438273680618584</v>
+        <v>1.53371947310052</v>
       </c>
       <c r="F17" t="n">
-        <v>7.801738588705014</v>
+        <v>1.267782520664565</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>20.88245850401167</v>
+        <v>3.393399506901897</v>
       </c>
       <c r="D18" t="n">
-        <v>22.81841792746959</v>
+        <v>3.707992913213809</v>
       </c>
       <c r="E18" t="n">
-        <v>9.438273680618584</v>
+        <v>1.53371947310052</v>
       </c>
       <c r="F18" t="n">
-        <v>7.801738588705014</v>
+        <v>1.267782520664565</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>24.07364295560271</v>
+        <v>3.911966980285441</v>
       </c>
       <c r="D19" t="n">
-        <v>25.77199419531783</v>
+        <v>4.187949056739148</v>
       </c>
       <c r="E19" t="n">
-        <v>9.438273680618584</v>
+        <v>1.53371947310052</v>
       </c>
       <c r="F19" t="n">
-        <v>7.801738588705014</v>
+        <v>1.267782520664565</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
